--- a/demo/image_metadata_with_llava_short.xlsx
+++ b/demo/image_metadata_with_llava_short.xlsx
@@ -486,10 +486,10 @@
         <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1702</v>
+        <v>17.0213</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1702</v>
+        <v>17.0213</v>
       </c>
     </row>
     <row r="3">
@@ -520,10 +520,10 @@
         <v>2.63</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1176</v>
+        <v>11.7647</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1176</v>
+        <v>11.7647</v>
       </c>
     </row>
     <row r="4">
@@ -554,10 +554,10 @@
         <v>3.96</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2051</v>
+        <v>20.5128</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1538</v>
+        <v>15.3846</v>
       </c>
     </row>
     <row r="5">
@@ -588,10 +588,10 @@
         <v>0.96</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1168</v>
+        <v>11.6788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0876</v>
+        <v>8.7591</v>
       </c>
     </row>
     <row r="6">
@@ -622,10 +622,10 @@
         <v>0.82</v>
       </c>
       <c r="G6" t="n">
-        <v>0.129</v>
+        <v>12.9032</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1075</v>
+        <v>10.7527</v>
       </c>
     </row>
     <row r="7">
@@ -690,10 +690,10 @@
         <v>0.73</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0882</v>
+        <v>8.823499999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0588</v>
+        <v>5.8824</v>
       </c>
     </row>
     <row r="9">
@@ -724,10 +724,10 @@
         <v>1.48</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1818</v>
+        <v>18.1818</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1039</v>
+        <v>10.3896</v>
       </c>
     </row>
     <row r="10">
@@ -758,10 +758,10 @@
         <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1833</v>
+        <v>18.3333</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1667</v>
+        <v>16.6667</v>
       </c>
     </row>
     <row r="11">
@@ -792,10 +792,10 @@
         <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1905</v>
+        <v>19.0476</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1429</v>
+        <v>14.2857</v>
       </c>
     </row>
     <row r="12">
@@ -826,10 +826,10 @@
         <v>0.99</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2022</v>
+        <v>20.2247</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08989999999999999</v>
+        <v>8.988799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -860,10 +860,10 @@
         <v>1.26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2087</v>
+        <v>20.8696</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1043</v>
+        <v>10.4348</v>
       </c>
     </row>
     <row r="14">
@@ -894,10 +894,10 @@
         <v>0.85</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
     </row>
     <row r="15">
@@ -928,10 +928,10 @@
         <v>2.78</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2667</v>
+        <v>26.6667</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1778</v>
+        <v>17.7778</v>
       </c>
     </row>
     <row r="16">
@@ -962,10 +962,10 @@
         <v>2.13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1569</v>
+        <v>15.6863</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1569</v>
+        <v>15.6863</v>
       </c>
     </row>
     <row r="17">
@@ -996,10 +996,10 @@
         <v>1.91</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1282</v>
+        <v>12.8205</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1282</v>
+        <v>12.8205</v>
       </c>
     </row>
     <row r="18">
@@ -1030,10 +1030,10 @@
         <v>2.71</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2143</v>
+        <v>21.4286</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1786</v>
+        <v>17.8571</v>
       </c>
     </row>
     <row r="19">
@@ -1064,10 +1064,10 @@
         <v>6.73</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2857</v>
+        <v>28.5714</v>
       </c>
     </row>
     <row r="20">
@@ -1098,10 +1098,10 @@
         <v>2.44</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2051</v>
+        <v>20.5128</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1026</v>
+        <v>10.2564</v>
       </c>
     </row>
     <row r="21">
@@ -1132,10 +1132,10 @@
         <v>2.09</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1887</v>
+        <v>18.8679</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1887</v>
+        <v>18.8679</v>
       </c>
     </row>
     <row r="22">
@@ -1166,10 +1166,10 @@
         <v>3.12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1647</v>
+        <v>16.4706</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1647</v>
+        <v>16.4706</v>
       </c>
     </row>
     <row r="23">
@@ -1200,10 +1200,10 @@
         <v>1.83</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1739</v>
+        <v>17.3913</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1217</v>
+        <v>12.1739</v>
       </c>
     </row>
     <row r="24">
@@ -1234,10 +1234,10 @@
         <v>4.5</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1268,10 +1268,10 @@
         <v>2.83</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1538</v>
+        <v>15.3846</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1538</v>
+        <v>15.3846</v>
       </c>
     </row>
     <row r="26">
@@ -1304,10 +1304,10 @@
         <v>2.65</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1754</v>
+        <v>17.5439</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1404</v>
+        <v>14.0351</v>
       </c>
     </row>
     <row r="27">
@@ -1338,10 +1338,10 @@
         <v>1.25</v>
       </c>
       <c r="G27" t="n">
-        <v>0.175</v>
+        <v>17.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0.125</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28">
@@ -1372,10 +1372,10 @@
         <v>1.01</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08989999999999999</v>
+        <v>8.988799999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08989999999999999</v>
+        <v>8.988799999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1406,10 +1406,10 @@
         <v>1.54</v>
       </c>
       <c r="G29" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1440,10 +1440,10 @@
         <v>1.48</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2083</v>
+        <v>20.8333</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1667</v>
+        <v>16.6667</v>
       </c>
     </row>
     <row r="31">
@@ -1474,10 +1474,10 @@
         <v>1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1772</v>
+        <v>17.7215</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1013</v>
+        <v>10.1266</v>
       </c>
     </row>
     <row r="32">
@@ -1508,10 +1508,10 @@
         <v>1.51</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1389</v>
+        <v>13.8889</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1389</v>
+        <v>13.8889</v>
       </c>
     </row>
     <row r="33">
@@ -1542,10 +1542,10 @@
         <v>1.1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1231</v>
+        <v>12.3077</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1231</v>
+        <v>12.3077</v>
       </c>
     </row>
     <row r="34">
@@ -1576,10 +1576,10 @@
         <v>0.87</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0583</v>
+        <v>5.8252</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0388</v>
+        <v>3.8835</v>
       </c>
     </row>
     <row r="35">
@@ -1610,10 +1610,10 @@
         <v>1.38</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1772</v>
+        <v>17.7215</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1519</v>
+        <v>15.1899</v>
       </c>
     </row>
     <row r="36">
@@ -1644,10 +1644,10 @@
         <v>2.14</v>
       </c>
       <c r="G36" t="n">
-        <v>0.12</v>
+        <v>12</v>
       </c>
       <c r="H36" t="n">
-        <v>0.08</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1678,10 +1678,10 @@
         <v>2.78</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2326</v>
+        <v>23.2558</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1395</v>
+        <v>13.9535</v>
       </c>
     </row>
     <row r="38">
@@ -1712,10 +1712,10 @@
         <v>3.05</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="39">
@@ -1746,10 +1746,10 @@
         <v>2.23</v>
       </c>
       <c r="G39" t="n">
-        <v>0.303</v>
+        <v>30.303</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1818</v>
+        <v>18.1818</v>
       </c>
     </row>
     <row r="40">
@@ -1780,10 +1780,10 @@
         <v>4.46</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3333</v>
+        <v>33.3333</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="41">
@@ -1814,10 +1814,10 @@
         <v>1.99</v>
       </c>
       <c r="G41" t="n">
-        <v>0.09760000000000001</v>
+        <v>9.7561</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09760000000000001</v>
+        <v>9.7561</v>
       </c>
     </row>
     <row r="42">
@@ -1848,10 +1848,10 @@
         <v>1.46</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2169</v>
+        <v>21.6867</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1687</v>
+        <v>16.8675</v>
       </c>
     </row>
     <row r="43">
@@ -1882,10 +1882,10 @@
         <v>1.76</v>
       </c>
       <c r="G43" t="n">
-        <v>0.125</v>
+        <v>12.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.125</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="44">
@@ -1916,10 +1916,10 @@
         <v>0.52</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0741</v>
+        <v>7.4074</v>
       </c>
     </row>
     <row r="45">
@@ -1950,10 +1950,10 @@
         <v>0.85</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0455</v>
+        <v>4.5455</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0455</v>
+        <v>4.5455</v>
       </c>
     </row>
     <row r="46">
@@ -2018,10 +2018,10 @@
         <v>0.99</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1356</v>
+        <v>13.5593</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1017</v>
+        <v>10.1695</v>
       </c>
     </row>
     <row r="48">
@@ -2052,10 +2052,10 @@
         <v>0.55</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0377</v>
+        <v>3.7736</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0377</v>
+        <v>3.7736</v>
       </c>
     </row>
     <row r="49">
@@ -2086,10 +2086,10 @@
         <v>1.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1622</v>
+        <v>16.2162</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1081</v>
+        <v>10.8108</v>
       </c>
     </row>
     <row r="50">
@@ -2120,10 +2120,10 @@
         <v>0.5</v>
       </c>
       <c r="G50" t="n">
-        <v>0.06320000000000001</v>
+        <v>6.3158</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06320000000000001</v>
+        <v>6.3158</v>
       </c>
     </row>
     <row r="51">
@@ -2154,10 +2154,10 @@
         <v>0.58</v>
       </c>
       <c r="G51" t="n">
-        <v>0.08450000000000001</v>
+        <v>8.450699999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0.08450000000000001</v>
+        <v>8.450699999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2188,10 +2188,10 @@
         <v>0.8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0779</v>
+        <v>7.7922</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0519</v>
+        <v>5.1948</v>
       </c>
     </row>
     <row r="53">
@@ -2222,10 +2222,10 @@
         <v>1.18</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1026</v>
+        <v>10.2564</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1026</v>
+        <v>10.2564</v>
       </c>
     </row>
     <row r="54">
@@ -2256,10 +2256,10 @@
         <v>1.36</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2264</v>
+        <v>22.6415</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2075</v>
+        <v>20.7547</v>
       </c>
     </row>
     <row r="55">
@@ -2290,10 +2290,10 @@
         <v>3.66</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2963</v>
+        <v>29.6296</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="56">
@@ -2324,10 +2324,10 @@
         <v>0.44</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0412</v>
+        <v>4.1237</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0412</v>
+        <v>4.1237</v>
       </c>
     </row>
     <row r="57">
@@ -2358,10 +2358,10 @@
         <v>2.18</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
     </row>
     <row r="58">
@@ -2392,10 +2392,10 @@
         <v>2.09</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2326</v>
+        <v>23.2558</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1395</v>
+        <v>13.9535</v>
       </c>
     </row>
     <row r="59">
@@ -2426,10 +2426,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0882</v>
+        <v>8.823499999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0882</v>
+        <v>8.823499999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2460,10 +2460,10 @@
         <v>5.96</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4722</v>
+        <v>47.2222</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3056</v>
+        <v>30.5556</v>
       </c>
     </row>
     <row r="61">
@@ -2528,10 +2528,10 @@
         <v>1.2</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0606</v>
+        <v>6.0606</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0606</v>
+        <v>6.0606</v>
       </c>
     </row>
     <row r="63">
@@ -2596,10 +2596,10 @@
         <v>1.29</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2105</v>
+        <v>21.0526</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2105</v>
+        <v>21.0526</v>
       </c>
     </row>
     <row r="65">
@@ -2630,10 +2630,10 @@
         <v>0.5</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0755</v>
+        <v>7.5472</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0566</v>
+        <v>5.6604</v>
       </c>
     </row>
     <row r="66">
@@ -2664,10 +2664,10 @@
         <v>2.91</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1481</v>
+        <v>14.8148</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1481</v>
+        <v>14.8148</v>
       </c>
     </row>
     <row r="67">
@@ -2732,10 +2732,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
       <c r="H68" t="n">
-        <v>0.08890000000000001</v>
+        <v>8.8889</v>
       </c>
     </row>
     <row r="69">
@@ -2834,10 +2834,10 @@
         <v>0.44</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0256</v>
+        <v>2.5641</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0256</v>
+        <v>2.5641</v>
       </c>
     </row>
     <row r="72">
@@ -2868,10 +2868,10 @@
         <v>1.54</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1765</v>
+        <v>17.6471</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1471</v>
+        <v>14.7059</v>
       </c>
     </row>
     <row r="73">
@@ -2902,10 +2902,10 @@
         <v>2.02</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2273</v>
+        <v>22.7273</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1818</v>
+        <v>18.1818</v>
       </c>
     </row>
     <row r="74">
@@ -2936,10 +2936,10 @@
         <v>1.28</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1266</v>
+        <v>12.6582</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1013</v>
+        <v>10.1266</v>
       </c>
     </row>
     <row r="75">
@@ -2970,10 +2970,10 @@
         <v>0.62</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0779</v>
+        <v>7.7922</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0519</v>
+        <v>5.1948</v>
       </c>
     </row>
     <row r="76">
@@ -3004,10 +3004,10 @@
         <v>1.87</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0556</v>
+        <v>5.5556</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0556</v>
+        <v>5.5556</v>
       </c>
     </row>
     <row r="77">
@@ -3038,10 +3038,10 @@
         <v>0.76</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0417</v>
+        <v>4.1667</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0417</v>
+        <v>4.1667</v>
       </c>
     </row>
     <row r="78">
@@ -3072,10 +3072,10 @@
         <v>2.13</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1667</v>
+        <v>16.6667</v>
       </c>
     </row>
     <row r="79">
@@ -3106,10 +3106,10 @@
         <v>2.66</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="80">
@@ -3140,10 +3140,10 @@
         <v>0.95</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1613</v>
+        <v>16.129</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0645</v>
+        <v>6.4516</v>
       </c>
     </row>
     <row r="81">
@@ -3174,10 +3174,10 @@
         <v>0.65</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0702</v>
+        <v>7.0175</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0702</v>
+        <v>7.0175</v>
       </c>
     </row>
     <row r="82">
@@ -3208,10 +3208,10 @@
         <v>1.72</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1739</v>
+        <v>17.3913</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1043</v>
+        <v>10.4348</v>
       </c>
     </row>
     <row r="83">
@@ -3242,10 +3242,10 @@
         <v>1.09</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0513</v>
+        <v>5.1282</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0513</v>
+        <v>5.1282</v>
       </c>
     </row>
     <row r="84">
@@ -3276,10 +3276,10 @@
         <v>13.46</v>
       </c>
       <c r="G84" t="n">
-        <v>0.375</v>
+        <v>37.5</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2917</v>
+        <v>29.1667</v>
       </c>
     </row>
     <row r="85">
@@ -3310,10 +3310,10 @@
         <v>1.48</v>
       </c>
       <c r="G85" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -3344,10 +3344,10 @@
         <v>0.47</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0392</v>
+        <v>3.9216</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0392</v>
+        <v>3.9216</v>
       </c>
     </row>
     <row r="87">
@@ -3378,10 +3378,10 @@
         <v>2.02</v>
       </c>
       <c r="G87" t="n">
-        <v>0.3111</v>
+        <v>31.1111</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1778</v>
+        <v>17.7778</v>
       </c>
     </row>
     <row r="88">
@@ -3412,10 +3412,10 @@
         <v>1.91</v>
       </c>
       <c r="G88" t="n">
-        <v>0.2034</v>
+        <v>20.339</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1695</v>
+        <v>16.9492</v>
       </c>
     </row>
     <row r="89">
@@ -3446,10 +3446,10 @@
         <v>0.72</v>
       </c>
       <c r="G89" t="n">
-        <v>0.06560000000000001</v>
+        <v>6.5574</v>
       </c>
       <c r="H89" t="n">
-        <v>0.06560000000000001</v>
+        <v>6.5574</v>
       </c>
     </row>
     <row r="90">
@@ -3514,10 +3514,10 @@
         <v>0.95</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1667</v>
+        <v>16.6667</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -3548,10 +3548,10 @@
         <v>1.53</v>
       </c>
       <c r="G92" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
       <c r="H92" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -3582,10 +3582,10 @@
         <v>2.69</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1235</v>
+        <v>12.3457</v>
       </c>
     </row>
     <row r="94">
@@ -3616,10 +3616,10 @@
         <v>2.66</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1818</v>
+        <v>18.1818</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1212</v>
+        <v>12.1212</v>
       </c>
     </row>
     <row r="95">
@@ -3650,10 +3650,10 @@
         <v>1.76</v>
       </c>
       <c r="G95" t="n">
-        <v>0.1053</v>
+        <v>10.5263</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1053</v>
+        <v>10.5263</v>
       </c>
     </row>
     <row r="96">
@@ -3684,10 +3684,10 @@
         <v>2.29</v>
       </c>
       <c r="G96" t="n">
-        <v>0.06900000000000001</v>
+        <v>6.8966</v>
       </c>
       <c r="H96" t="n">
-        <v>0.06900000000000001</v>
+        <v>6.8966</v>
       </c>
     </row>
     <row r="97">
@@ -3718,10 +3718,10 @@
         <v>6.09</v>
       </c>
       <c r="G97" t="n">
-        <v>0.2569</v>
+        <v>25.6881</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1835</v>
+        <v>18.3486</v>
       </c>
     </row>
     <row r="98">
@@ -3752,10 +3752,10 @@
         <v>1.04</v>
       </c>
       <c r="G98" t="n">
-        <v>0.1613</v>
+        <v>16.129</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1129</v>
+        <v>11.2903</v>
       </c>
     </row>
     <row r="99">
@@ -3786,10 +3786,10 @@
         <v>1.42</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2432</v>
+        <v>24.3243</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1622</v>
+        <v>16.2162</v>
       </c>
     </row>
     <row r="100">
@@ -3820,10 +3820,10 @@
         <v>3.87</v>
       </c>
       <c r="G100" t="n">
-        <v>0.259</v>
+        <v>25.8993</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2014</v>
+        <v>20.1439</v>
       </c>
     </row>
     <row r="101">
@@ -3854,10 +3854,10 @@
         <v>1.17</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1167</v>
+        <v>11.6667</v>
       </c>
     </row>
     <row r="102">
@@ -3888,10 +3888,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G102" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1111</v>
+        <v>11.1111</v>
       </c>
     </row>
     <row r="103">
@@ -3922,10 +3922,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>0.1399</v>
+        <v>13.986</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0839</v>
+        <v>8.3916</v>
       </c>
     </row>
     <row r="104">
@@ -3956,10 +3956,10 @@
         <v>1.42</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2295</v>
+        <v>22.9508</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0984</v>
+        <v>9.8361</v>
       </c>
     </row>
     <row r="105">
@@ -3990,10 +3990,10 @@
         <v>0.76</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1556</v>
+        <v>15.5556</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0667</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="106">
@@ -4024,10 +4024,10 @@
         <v>2.01</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2667</v>
+        <v>26.6667</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1333</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="107">
@@ -4058,10 +4058,10 @@
         <v>3.41</v>
       </c>
       <c r="G107" t="n">
-        <v>0.2222</v>
+        <v>22.2222</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0988</v>
+        <v>9.8765</v>
       </c>
     </row>
     <row r="108">
@@ -4092,10 +4092,10 @@
         <v>2.34</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3023</v>
+        <v>30.2326</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1628</v>
+        <v>16.2791</v>
       </c>
     </row>
     <row r="109">
@@ -4126,10 +4126,10 @@
         <v>1.36</v>
       </c>
       <c r="G109" t="n">
-        <v>0.2243</v>
+        <v>22.4299</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1308</v>
+        <v>13.0841</v>
       </c>
     </row>
     <row r="110">
@@ -4160,10 +4160,10 @@
         <v>1.26</v>
       </c>
       <c r="G110" t="n">
-        <v>0.2124</v>
+        <v>21.2389</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1416</v>
+        <v>14.1593</v>
       </c>
     </row>
     <row r="111">
@@ -4194,10 +4194,10 @@
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.1912</v>
+        <v>19.1176</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1176</v>
+        <v>11.7647</v>
       </c>
     </row>
     <row r="112">
@@ -4228,10 +4228,10 @@
         <v>1.57</v>
       </c>
       <c r="G112" t="n">
-        <v>0.1488</v>
+        <v>14.876</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1157</v>
+        <v>11.5702</v>
       </c>
     </row>
     <row r="113">
@@ -4262,10 +4262,10 @@
         <v>2.52</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1818</v>
+        <v>18.1818</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1212</v>
+        <v>12.1212</v>
       </c>
     </row>
     <row r="114">
@@ -4296,10 +4296,10 @@
         <v>1.81</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1739</v>
+        <v>17.3913</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1449</v>
+        <v>14.4928</v>
       </c>
     </row>
     <row r="115">
@@ -4330,10 +4330,10 @@
         <v>2.87</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1151</v>
+        <v>11.5108</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1151</v>
+        <v>11.5108</v>
       </c>
     </row>
     <row r="116">
@@ -4364,10 +4364,10 @@
         <v>5.01</v>
       </c>
       <c r="G116" t="n">
-        <v>0.3273</v>
+        <v>32.7273</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2545</v>
+        <v>25.4545</v>
       </c>
     </row>
     <row r="117">
@@ -4398,10 +4398,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>0.1505</v>
+        <v>15.0538</v>
       </c>
       <c r="H117" t="n">
-        <v>0.08599999999999999</v>
+        <v>8.6022</v>
       </c>
     </row>
     <row r="118">
@@ -4432,10 +4432,10 @@
         <v>1.63</v>
       </c>
       <c r="G118" t="n">
-        <v>0.1798</v>
+        <v>17.9775</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1124</v>
+        <v>11.236</v>
       </c>
     </row>
     <row r="119">
@@ -4466,10 +4466,10 @@
         <v>2.61</v>
       </c>
       <c r="G119" t="n">
-        <v>0.2474</v>
+        <v>24.7423</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1649</v>
+        <v>16.4948</v>
       </c>
     </row>
     <row r="120">
@@ -4500,10 +4500,10 @@
         <v>1.35</v>
       </c>
       <c r="G120" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
       <c r="H120" t="n">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121">
@@ -4534,10 +4534,10 @@
         <v>1.46</v>
       </c>
       <c r="G121" t="n">
-        <v>0.208</v>
+        <v>20.8</v>
       </c>
       <c r="H121" t="n">
-        <v>0.128</v>
+        <v>12.8</v>
       </c>
     </row>
   </sheetData>

--- a/demo/image_metadata_with_llava_short.xlsx
+++ b/demo/image_metadata_with_llava_short.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,16 @@
           <t>ROUGE-L_F</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>BERTScore</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>CLIPScore</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -491,6 +501,12 @@
       <c r="H2" t="n">
         <v>17.0213</v>
       </c>
+      <c r="I2" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -525,6 +541,12 @@
       <c r="H3" t="n">
         <v>11.7647</v>
       </c>
+      <c r="I3" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -559,6 +581,12 @@
       <c r="H4" t="n">
         <v>15.3846</v>
       </c>
+      <c r="I4" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -593,6 +621,12 @@
       <c r="H5" t="n">
         <v>8.7591</v>
       </c>
+      <c r="I5" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,6 +661,12 @@
       <c r="H6" t="n">
         <v>10.7527</v>
       </c>
+      <c r="I6" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -661,6 +701,12 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -695,6 +741,12 @@
       <c r="H8" t="n">
         <v>5.8824</v>
       </c>
+      <c r="I8" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -729,6 +781,12 @@
       <c r="H9" t="n">
         <v>10.3896</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -763,6 +821,12 @@
       <c r="H10" t="n">
         <v>16.6667</v>
       </c>
+      <c r="I10" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -797,6 +861,12 @@
       <c r="H11" t="n">
         <v>14.2857</v>
       </c>
+      <c r="I11" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -831,6 +901,12 @@
       <c r="H12" t="n">
         <v>8.988799999999999</v>
       </c>
+      <c r="I12" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -865,6 +941,12 @@
       <c r="H13" t="n">
         <v>10.4348</v>
       </c>
+      <c r="I13" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -899,6 +981,12 @@
       <c r="H14" t="n">
         <v>7.4074</v>
       </c>
+      <c r="I14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -933,6 +1021,12 @@
       <c r="H15" t="n">
         <v>17.7778</v>
       </c>
+      <c r="I15" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -967,6 +1061,12 @@
       <c r="H16" t="n">
         <v>15.6863</v>
       </c>
+      <c r="I16" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1001,6 +1101,12 @@
       <c r="H17" t="n">
         <v>12.8205</v>
       </c>
+      <c r="I17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1035,6 +1141,12 @@
       <c r="H18" t="n">
         <v>17.8571</v>
       </c>
+      <c r="I18" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1069,6 +1181,12 @@
       <c r="H19" t="n">
         <v>28.5714</v>
       </c>
+      <c r="I19" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1103,6 +1221,12 @@
       <c r="H20" t="n">
         <v>10.2564</v>
       </c>
+      <c r="I20" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1137,6 +1261,12 @@
       <c r="H21" t="n">
         <v>18.8679</v>
       </c>
+      <c r="I21" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1171,6 +1301,12 @@
       <c r="H22" t="n">
         <v>16.4706</v>
       </c>
+      <c r="I22" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1205,6 +1341,12 @@
       <c r="H23" t="n">
         <v>12.1739</v>
       </c>
+      <c r="I23" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1239,6 +1381,12 @@
       <c r="H24" t="n">
         <v>20</v>
       </c>
+      <c r="I24" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1272,6 +1420,12 @@
       </c>
       <c r="H25" t="n">
         <v>15.3846</v>
+      </c>
+      <c r="I25" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1309,6 +1463,12 @@
       <c r="H26" t="n">
         <v>14.0351</v>
       </c>
+      <c r="I26" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1343,6 +1503,12 @@
       <c r="H27" t="n">
         <v>12.5</v>
       </c>
+      <c r="I27" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1377,6 +1543,12 @@
       <c r="H28" t="n">
         <v>8.988799999999999</v>
       </c>
+      <c r="I28" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1411,6 +1583,12 @@
       <c r="H29" t="n">
         <v>10</v>
       </c>
+      <c r="I29" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1445,6 +1623,12 @@
       <c r="H30" t="n">
         <v>16.6667</v>
       </c>
+      <c r="I30" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1479,6 +1663,12 @@
       <c r="H31" t="n">
         <v>10.1266</v>
       </c>
+      <c r="I31" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1513,6 +1703,12 @@
       <c r="H32" t="n">
         <v>13.8889</v>
       </c>
+      <c r="I32" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J32" t="n">
+        <v>30.05</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1547,6 +1743,12 @@
       <c r="H33" t="n">
         <v>12.3077</v>
       </c>
+      <c r="I33" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1581,6 +1783,12 @@
       <c r="H34" t="n">
         <v>3.8835</v>
       </c>
+      <c r="I34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1615,6 +1823,12 @@
       <c r="H35" t="n">
         <v>15.1899</v>
       </c>
+      <c r="I35" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1649,6 +1863,12 @@
       <c r="H36" t="n">
         <v>8</v>
       </c>
+      <c r="I36" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1683,6 +1903,12 @@
       <c r="H37" t="n">
         <v>13.9535</v>
       </c>
+      <c r="I37" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="J37" t="n">
+        <v>32.87</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1717,6 +1943,12 @@
       <c r="H38" t="n">
         <v>22.2222</v>
       </c>
+      <c r="I38" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="J38" t="n">
+        <v>22.71</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1751,6 +1983,12 @@
       <c r="H39" t="n">
         <v>18.1818</v>
       </c>
+      <c r="I39" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1785,6 +2023,12 @@
       <c r="H40" t="n">
         <v>22.2222</v>
       </c>
+      <c r="I40" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1819,6 +2063,12 @@
       <c r="H41" t="n">
         <v>9.7561</v>
       </c>
+      <c r="I41" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>32.06</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1853,6 +2103,12 @@
       <c r="H42" t="n">
         <v>16.8675</v>
       </c>
+      <c r="I42" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1887,6 +2143,12 @@
       <c r="H43" t="n">
         <v>12.5</v>
       </c>
+      <c r="I43" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1921,6 +2183,12 @@
       <c r="H44" t="n">
         <v>7.4074</v>
       </c>
+      <c r="I44" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1955,6 +2223,12 @@
       <c r="H45" t="n">
         <v>4.5455</v>
       </c>
+      <c r="I45" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1989,6 +2263,12 @@
       <c r="H46" t="n">
         <v>0</v>
       </c>
+      <c r="I46" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2023,6 +2303,12 @@
       <c r="H47" t="n">
         <v>10.1695</v>
       </c>
+      <c r="I47" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2057,6 +2343,12 @@
       <c r="H48" t="n">
         <v>3.7736</v>
       </c>
+      <c r="I48" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2091,6 +2383,12 @@
       <c r="H49" t="n">
         <v>10.8108</v>
       </c>
+      <c r="I49" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2125,6 +2423,12 @@
       <c r="H50" t="n">
         <v>6.3158</v>
       </c>
+      <c r="I50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2159,6 +2463,12 @@
       <c r="H51" t="n">
         <v>8.450699999999999</v>
       </c>
+      <c r="I51" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2193,6 +2503,12 @@
       <c r="H52" t="n">
         <v>5.1948</v>
       </c>
+      <c r="I52" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2227,6 +2543,12 @@
       <c r="H53" t="n">
         <v>10.2564</v>
       </c>
+      <c r="I53" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2261,6 +2583,12 @@
       <c r="H54" t="n">
         <v>20.7547</v>
       </c>
+      <c r="I54" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2295,6 +2623,12 @@
       <c r="H55" t="n">
         <v>22.2222</v>
       </c>
+      <c r="I55" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2329,6 +2663,12 @@
       <c r="H56" t="n">
         <v>4.1237</v>
       </c>
+      <c r="I56" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2363,6 +2703,12 @@
       <c r="H57" t="n">
         <v>11.1111</v>
       </c>
+      <c r="I57" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2397,6 +2743,12 @@
       <c r="H58" t="n">
         <v>13.9535</v>
       </c>
+      <c r="I58" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2431,6 +2783,12 @@
       <c r="H59" t="n">
         <v>8.823499999999999</v>
       </c>
+      <c r="I59" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2465,6 +2823,12 @@
       <c r="H60" t="n">
         <v>30.5556</v>
       </c>
+      <c r="I60" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2499,6 +2863,12 @@
       <c r="H61" t="n">
         <v>0</v>
       </c>
+      <c r="I61" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2533,6 +2903,12 @@
       <c r="H62" t="n">
         <v>6.0606</v>
       </c>
+      <c r="I62" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="J62" t="n">
+        <v>23.38</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2567,6 +2943,12 @@
       <c r="H63" t="n">
         <v>0</v>
       </c>
+      <c r="I63" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2601,6 +2983,12 @@
       <c r="H64" t="n">
         <v>21.0526</v>
       </c>
+      <c r="I64" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2635,6 +3023,12 @@
       <c r="H65" t="n">
         <v>5.6604</v>
       </c>
+      <c r="I65" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2669,6 +3063,12 @@
       <c r="H66" t="n">
         <v>14.8148</v>
       </c>
+      <c r="I66" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2703,6 +3103,12 @@
       <c r="H67" t="n">
         <v>0</v>
       </c>
+      <c r="I67" t="n">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2737,6 +3143,12 @@
       <c r="H68" t="n">
         <v>8.8889</v>
       </c>
+      <c r="I68" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2771,6 +3183,12 @@
       <c r="H69" t="n">
         <v>0</v>
       </c>
+      <c r="I69" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2805,6 +3223,12 @@
       <c r="H70" t="n">
         <v>0</v>
       </c>
+      <c r="I70" t="n">
+        <v>-13.12</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2839,6 +3263,12 @@
       <c r="H71" t="n">
         <v>2.5641</v>
       </c>
+      <c r="I71" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2873,6 +3303,12 @@
       <c r="H72" t="n">
         <v>14.7059</v>
       </c>
+      <c r="I72" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2907,6 +3343,12 @@
       <c r="H73" t="n">
         <v>18.1818</v>
       </c>
+      <c r="I73" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2941,6 +3383,12 @@
       <c r="H74" t="n">
         <v>10.1266</v>
       </c>
+      <c r="I74" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2975,6 +3423,12 @@
       <c r="H75" t="n">
         <v>5.1948</v>
       </c>
+      <c r="I75" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3009,6 +3463,12 @@
       <c r="H76" t="n">
         <v>5.5556</v>
       </c>
+      <c r="I76" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3043,6 +3503,12 @@
       <c r="H77" t="n">
         <v>4.1667</v>
       </c>
+      <c r="I77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3077,6 +3543,12 @@
       <c r="H78" t="n">
         <v>16.6667</v>
       </c>
+      <c r="I78" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3111,6 +3583,12 @@
       <c r="H79" t="n">
         <v>22.2222</v>
       </c>
+      <c r="I79" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3145,6 +3623,12 @@
       <c r="H80" t="n">
         <v>6.4516</v>
       </c>
+      <c r="I80" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3179,6 +3663,12 @@
       <c r="H81" t="n">
         <v>7.0175</v>
       </c>
+      <c r="I81" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3213,6 +3703,12 @@
       <c r="H82" t="n">
         <v>10.4348</v>
       </c>
+      <c r="I82" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3247,6 +3743,12 @@
       <c r="H83" t="n">
         <v>5.1282</v>
       </c>
+      <c r="I83" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3281,6 +3783,12 @@
       <c r="H84" t="n">
         <v>29.1667</v>
       </c>
+      <c r="I84" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3315,6 +3823,12 @@
       <c r="H85" t="n">
         <v>20</v>
       </c>
+      <c r="I85" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3349,6 +3863,12 @@
       <c r="H86" t="n">
         <v>3.9216</v>
       </c>
+      <c r="I86" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3383,6 +3903,12 @@
       <c r="H87" t="n">
         <v>17.7778</v>
       </c>
+      <c r="I87" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="J87" t="n">
+        <v>29.85</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3417,6 +3943,12 @@
       <c r="H88" t="n">
         <v>16.9492</v>
       </c>
+      <c r="I88" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3451,6 +3983,12 @@
       <c r="H89" t="n">
         <v>6.5574</v>
       </c>
+      <c r="I89" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="J89" t="n">
+        <v>30.53</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3485,6 +4023,12 @@
       <c r="H90" t="n">
         <v>0</v>
       </c>
+      <c r="I90" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>27.58</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3519,6 +4063,12 @@
       <c r="H91" t="n">
         <v>10</v>
       </c>
+      <c r="I91" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="J91" t="n">
+        <v>28.92</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3553,6 +4103,12 @@
       <c r="H92" t="n">
         <v>15</v>
       </c>
+      <c r="I92" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="J92" t="n">
+        <v>39.69</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3587,6 +4143,12 @@
       <c r="H93" t="n">
         <v>12.3457</v>
       </c>
+      <c r="I93" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3621,6 +4183,12 @@
       <c r="H94" t="n">
         <v>12.1212</v>
       </c>
+      <c r="I94" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="J94" t="n">
+        <v>30.47</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3655,6 +4223,12 @@
       <c r="H95" t="n">
         <v>10.5263</v>
       </c>
+      <c r="I95" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3689,6 +4263,12 @@
       <c r="H96" t="n">
         <v>6.8966</v>
       </c>
+      <c r="I96" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3723,6 +4303,12 @@
       <c r="H97" t="n">
         <v>18.3486</v>
       </c>
+      <c r="I97" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3757,6 +4343,12 @@
       <c r="H98" t="n">
         <v>11.2903</v>
       </c>
+      <c r="I98" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3791,6 +4383,12 @@
       <c r="H99" t="n">
         <v>16.2162</v>
       </c>
+      <c r="I99" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3825,6 +4423,12 @@
       <c r="H100" t="n">
         <v>20.1439</v>
       </c>
+      <c r="I100" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3859,6 +4463,12 @@
       <c r="H101" t="n">
         <v>11.6667</v>
       </c>
+      <c r="I101" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3893,6 +4503,12 @@
       <c r="H102" t="n">
         <v>11.1111</v>
       </c>
+      <c r="I102" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3927,6 +4543,12 @@
       <c r="H103" t="n">
         <v>8.3916</v>
       </c>
+      <c r="I103" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3961,6 +4583,12 @@
       <c r="H104" t="n">
         <v>9.8361</v>
       </c>
+      <c r="I104" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3995,6 +4623,12 @@
       <c r="H105" t="n">
         <v>6.6667</v>
       </c>
+      <c r="I105" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4029,6 +4663,12 @@
       <c r="H106" t="n">
         <v>13.3333</v>
       </c>
+      <c r="I106" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4063,6 +4703,12 @@
       <c r="H107" t="n">
         <v>9.8765</v>
       </c>
+      <c r="I107" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4097,6 +4743,12 @@
       <c r="H108" t="n">
         <v>16.2791</v>
       </c>
+      <c r="I108" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4131,6 +4783,12 @@
       <c r="H109" t="n">
         <v>13.0841</v>
       </c>
+      <c r="I109" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4165,6 +4823,12 @@
       <c r="H110" t="n">
         <v>14.1593</v>
       </c>
+      <c r="I110" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4199,6 +4863,12 @@
       <c r="H111" t="n">
         <v>11.7647</v>
       </c>
+      <c r="I111" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4233,6 +4903,12 @@
       <c r="H112" t="n">
         <v>11.5702</v>
       </c>
+      <c r="I112" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4267,6 +4943,12 @@
       <c r="H113" t="n">
         <v>12.1212</v>
       </c>
+      <c r="I113" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4301,6 +4983,12 @@
       <c r="H114" t="n">
         <v>14.4928</v>
       </c>
+      <c r="I114" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4335,6 +5023,12 @@
       <c r="H115" t="n">
         <v>11.5108</v>
       </c>
+      <c r="I115" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4369,6 +5063,12 @@
       <c r="H116" t="n">
         <v>25.4545</v>
       </c>
+      <c r="I116" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4403,6 +5103,12 @@
       <c r="H117" t="n">
         <v>8.6022</v>
       </c>
+      <c r="I117" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4437,6 +5143,12 @@
       <c r="H118" t="n">
         <v>11.236</v>
       </c>
+      <c r="I118" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4471,6 +5183,12 @@
       <c r="H119" t="n">
         <v>16.4948</v>
       </c>
+      <c r="I119" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4505,6 +5223,12 @@
       <c r="H120" t="n">
         <v>16</v>
       </c>
+      <c r="I120" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4538,6 +5262,12 @@
       </c>
       <c r="H121" t="n">
         <v>12.8</v>
+      </c>
+      <c r="I121" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
